--- a/output/full_scan/batch_seq6_2026-06-25.xlsx
+++ b/output/full_scan/batch_seq6_2026-06-25.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O115"/>
+  <dimension ref="A1:O118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -951,21 +951,21 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6175</v>
+        <v>6173</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>立敦</t>
+          <t>信昌電</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>677.1913473965302</v>
+        <v>684.7918572973711</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>116.5</v>
+        <v>306.5</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,16 +976,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>65.43093019627132</v>
+        <v>68.69078689969977</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>41.40742094919141</v>
+        <v>40.97526369326416</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>1.154414577267885</v>
+        <v>0.1335132305940144</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L10" s="2" t="n">
         <v>0</v>
@@ -994,31 +994,31 @@
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.3643211558798427</v>
+        <v>0.5190571090656775</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>6209</v>
+        <v>6175</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>今國光</t>
+          <t>立敦</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>674.4640655658786</v>
+        <v>677.1913473965302</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>116.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>56.02061684240645</v>
+        <v>65.43093019627132</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>39.67078183940929</v>
+        <v>41.40742094919141</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.6726735055262606</v>
+        <v>1.154414577267885</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>-0.2874648167926255</v>
+        <v>0.3643211558798427</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>6166</v>
+        <v>6209</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>凌華</t>
+          <t>今國光</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>673.8968310562387</v>
+        <v>674.4640655658786</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>147</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,13 +1082,13 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>61.48818201954876</v>
+        <v>56.02061684240645</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>61.70443123739186</v>
+        <v>39.67078183940929</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.7645538212516273</v>
+        <v>0.6726735055262606</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>0</v>
@@ -1100,7 +1100,7 @@
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>0.2506546114433696</v>
+        <v>-0.2874648167926255</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -1110,21 +1110,21 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>6207</v>
+        <v>6166</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>雷科</t>
+          <t>凌華</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>673.715420445879</v>
+        <v>673.8968310562387</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>154.5</v>
+        <v>147</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,13 +1135,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>64.00034260932222</v>
+        <v>61.48818201954876</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>64.61540729260439</v>
+        <v>61.70443123739186</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.376362528399884</v>
+        <v>0.7645538212516273</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>-0.0153798265104825</v>
+        <v>0.2506546114433696</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1163,21 +1163,21 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>6168</v>
+        <v>6207</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>宏齊</t>
+          <t>雷科</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>670.4496456868688</v>
+        <v>673.715420445879</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>32.8</v>
+        <v>154.5</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>63.01643319996423</v>
+        <v>64.00034260932222</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>26.17262707841248</v>
+        <v>64.61540729260439</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.678343489685304</v>
+        <v>0.376362528399884</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>0.8901985031183448</v>
+        <v>-0.0153798265104825</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6196</v>
+        <v>6168</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>帆宣</t>
+          <t>宏齊</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>669.5087111730184</v>
+        <v>670.4496456868688</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>559</v>
+        <v>32.8</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,13 +1241,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>63.48543140674025</v>
+        <v>63.01643319996423</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>37.79841462665058</v>
+        <v>26.17262707841248</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.7072122926331892</v>
+        <v>1.678343489685304</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-2.212024037802166</v>
+        <v>0.8901985031183448</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>6465</v>
+        <v>6196</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>威潤</t>
+          <t>帆宣</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>658.0522887157515</v>
+        <v>669.5087111730184</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>67</v>
+        <v>559</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>63.50434690907051</v>
+        <v>63.48543140674025</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>33.74226257433484</v>
+        <v>37.79841462665058</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>0.4370456351473438</v>
+        <v>0.7072122926331892</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>0</v>
@@ -1312,7 +1312,7 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.7872291429078988</v>
+        <v>-2.212024037802166</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1322,21 +1322,21 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6208</v>
+        <v>6465</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>日揚</t>
+          <t>威潤</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>653.6217021733654</v>
+        <v>658.0522887157515</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,13 +1347,13 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>61.29932106193442</v>
+        <v>63.50434690907051</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>23.97035923762248</v>
+        <v>33.74226257433484</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.878143603659373</v>
+        <v>0.4370456351473438</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>1.717308324827345</v>
+        <v>0.7872291429078988</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>6446</v>
+        <v>6208</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>藥華藥</t>
+          <t>日揚</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>635.9985597857379</v>
+        <v>653.6217021733654</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1195</v>
+        <v>105</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>82.27161945657298</v>
+        <v>61.29932106193442</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45.58854819940581</v>
+        <v>23.97035923762248</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8534470270130869</v>
+        <v>1.878143603659373</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>15.76469300773799</v>
+        <v>1.717308324827345</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6220</v>
+        <v>6241</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>岳豐</t>
+          <t>鑫永洋</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>632.791345380154</v>
+        <v>653.2406794286284</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>39.3</v>
+        <v>16.15</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>67.72560640170678</v>
+        <v>81.43335612625421</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>58.52157786996685</v>
+        <v>41.90009164801991</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.5480567030502809</v>
+        <v>1.42406794286284</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.445936198553672</v>
+        <v>0.3686813215995035</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6257</v>
+        <v>6446</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>矽格</t>
+          <t>藥華藥</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>626.8177394709393</v>
+        <v>635.9985597857379</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>238</v>
+        <v>1195</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>59.85740496685461</v>
+        <v>82.27161945657298</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>26.70620791710761</v>
+        <v>45.58854819940581</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>1.093159374302127</v>
+        <v>0.8534470270130869</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>1.639172110506024</v>
+        <v>15.76469300773799</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6292</v>
+        <v>6220</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>迅德</t>
+          <t>岳豐</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>618.2551476399085</v>
+        <v>632.791345380154</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>60.8</v>
+        <v>39.3</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,13 +1559,13 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>50.10795652495951</v>
+        <v>67.72560640170678</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>31.89983937289998</v>
+        <v>58.52157786996685</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.2477350431787133</v>
+        <v>0.5480567030502809</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>-0.5797825585678988</v>
+        <v>0.445936198553672</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>6204</v>
+        <v>6257</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>艾華</t>
+          <t>矽格</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>610.0360108258393</v>
+        <v>626.8177394709393</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>125</v>
+        <v>238</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>70.88074019585355</v>
+        <v>59.85740496685461</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>40.04721372216538</v>
+        <v>26.70620791710761</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.9159320006852464</v>
+        <v>1.093159374302127</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.7133819591601025</v>
+        <v>1.639172110506024</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6239</v>
+        <v>6292</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>迅德</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>607.4025131662281</v>
+        <v>618.2551476399085</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>326</v>
+        <v>60.8</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>51.39973003563419</v>
+        <v>50.10795652495951</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>30.76922613410838</v>
+        <v>31.89983937289998</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.103925283975921</v>
+        <v>0.2477350431787133</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,7 +1683,7 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>-4.580413327564862</v>
+        <v>-0.5797825585678988</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1693,21 +1693,21 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6409</v>
+        <v>6204</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>旭隼</t>
+          <t>艾華</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>605.1571148400429</v>
+        <v>610.0360108258393</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1000</v>
+        <v>125</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>68.41350125110439</v>
+        <v>70.88074019585355</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>39.06829108919285</v>
+        <v>40.04721372216538</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.280914633576618</v>
+        <v>0.9159320006852464</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>7.190537801085242</v>
+        <v>0.7133819591601025</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>6411</v>
+        <v>6239</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>晶焱</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>597.372202656902</v>
+        <v>607.4025131662281</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>102</v>
+        <v>326</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>54.61724827214827</v>
+        <v>51.39973003563419</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>31.13967943644101</v>
+        <v>30.76922613410838</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.4113886734401755</v>
+        <v>1.103925283975921</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.2539077427246767</v>
+        <v>-4.580413327564862</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1799,21 +1799,21 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>6189</v>
+        <v>6409</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>豐藝</t>
+          <t>旭隼</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>584.0599365920879</v>
+        <v>605.1571148400429</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>50.5</v>
+        <v>1000</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>43.95523733594828</v>
+        <v>68.41350125110439</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>25.55106540907467</v>
+        <v>39.06829108919285</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.4740688723482259</v>
+        <v>1.280914633576618</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>-0.463135991456215</v>
+        <v>7.190537801085242</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6174</v>
+        <v>6411</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>安碁</t>
+          <t>晶焱</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>581.4446265445182</v>
+        <v>597.372202656902</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>49.3</v>
+        <v>102</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.05827958361861</v>
+        <v>54.61724827214827</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>35.13532167091937</v>
+        <v>31.13967943644101</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.2628300987477468</v>
+        <v>0.4113886734401755</v>
       </c>
       <c r="K27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>-0.5853400995792692</v>
+        <v>0.2539077427246767</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6223</v>
+        <v>6189</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>旺矽</t>
+          <t>豐藝</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>578.0292389130242</v>
+        <v>584.0599365920879</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>6905</v>
+        <v>50.5</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>64.49780498889209</v>
+        <v>43.95523733594828</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>25.85683373621633</v>
+        <v>25.55106540907467</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.602526453612655</v>
+        <v>0.4740688723482259</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>59.65220500083967</v>
+        <v>-0.463135991456215</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6202</v>
+        <v>6174</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>盛群</t>
+          <t>安碁</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>573.4482507514298</v>
+        <v>581.4446265445182</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>70.40000000000001</v>
+        <v>49.3</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>63.99202951798695</v>
+        <v>55.05827958361861</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>29.22183664192221</v>
+        <v>35.13532167091937</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.965800451011026</v>
+        <v>0.2628300987477468</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>1.444941074376926</v>
+        <v>-0.5853400995792692</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6190</v>
+        <v>6223</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>萬泰科</t>
+          <t>旺矽</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>570.0926083341826</v>
+        <v>578.0292389130242</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>83.40000000000001</v>
+        <v>6905</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.44504081663376</v>
+        <v>64.49780498889209</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>23.82025292967639</v>
+        <v>25.85683373621633</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.4921426294352204</v>
+        <v>0.602526453612655</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,7 +2054,7 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1177928606167659</v>
+        <v>59.65220500083967</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2064,21 +2064,21 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>6451</v>
+        <v>6202</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>訊芯-KY</t>
+          <t>盛群</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>569.0227516502836</v>
+        <v>573.4482507514298</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>614</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,13 +2089,13 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.87197646914061</v>
+        <v>63.99202951798695</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>33.49629310751178</v>
+        <v>29.22183664192221</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>1.386402579872613</v>
+        <v>0.965800451011026</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>0</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.6189743027237853</v>
+        <v>1.444941074376926</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2117,21 +2117,21 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>6237</v>
+        <v>6190</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>驊訊</t>
+          <t>萬泰科</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>567.3263788464581</v>
+        <v>570.0926083341826</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>49.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>55.89131337477297</v>
+        <v>56.44504081663376</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>20.73478609910982</v>
+        <v>23.82025292967639</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.9799752513777716</v>
+        <v>0.4921426294352204</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.0571287623542922</v>
+        <v>-0.1177928606167659</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2170,21 +2170,21 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>6243</v>
+        <v>6451</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>迅杰</t>
+          <t>訊芯-KY</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>567.0172202749038</v>
+        <v>569.0227516502836</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44.2</v>
+        <v>614</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>73.85456122119174</v>
+        <v>55.87197646914061</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>31.07125761600527</v>
+        <v>33.49629310751178</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.001722027490381</v>
+        <v>1.386402579872613</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.547654402241493</v>
+        <v>-0.6189743027237853</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>6259</v>
+        <v>6237</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>百徽</t>
+          <t>驊訊</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>554.5081085037287</v>
+        <v>567.3263788464581</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>38.15</v>
+        <v>49.3</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>68.25648276423853</v>
+        <v>55.89131337477297</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>49.20495334032126</v>
+        <v>20.73478609910982</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.4066852589441315</v>
+        <v>0.9799752513777716</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.7489769513643889</v>
+        <v>-0.0571287623542922</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2276,21 +2276,21 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>6185</v>
+        <v>6243</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>幃翔</t>
+          <t>迅杰</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>551.1842840897746</v>
+        <v>567.0172202749038</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>14.5</v>
+        <v>44.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>56.43426022070224</v>
+        <v>73.85456122119174</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.61466078293125</v>
+        <v>31.07125761600527</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.9184284089774588</v>
+        <v>3.001722027490381</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.0301266391686151</v>
+        <v>1.547654402241493</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6472</v>
+        <v>6259</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>保瑞</t>
+          <t>百徽</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>546.2936272528927</v>
+        <v>554.5081085037287</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>419.5</v>
+        <v>38.15</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,13 +2354,13 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>57.08029049832422</v>
+        <v>68.25648276423853</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>26.47075290394785</v>
+        <v>49.20495334032126</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.101842003494973</v>
+        <v>0.4066852589441315</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>6.435581685770009</v>
+        <v>0.7489769513643889</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>6435</v>
+        <v>6185</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>大中</t>
+          <t>幃翔</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>536.8161997127337</v>
+        <v>551.1842840897746</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>353.5</v>
+        <v>14.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>72.12742295648351</v>
+        <v>56.43426022070224</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>32.66970268869157</v>
+        <v>17.61466078293125</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.090330959729416</v>
+        <v>0.9184284089774588</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>6.599392214839721</v>
+        <v>0.0301266391686151</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>6449</v>
+        <v>6472</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>鈺邦</t>
+          <t>保瑞</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>533.1466766103759</v>
+        <v>546.2936272528927</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>371</v>
+        <v>419.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>51.78281865712357</v>
+        <v>57.08029049832422</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>35.93020622556805</v>
+        <v>26.47075290394785</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.651339635642737</v>
+        <v>1.101842003494973</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>-10.26968174185765</v>
+        <v>6.435581685770009</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>6265</v>
+        <v>6435</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>方土昶</t>
+          <t>大中</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>532.4245968299225</v>
+        <v>536.8161997127337</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>55</v>
+        <v>353.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>51.23046644998228</v>
+        <v>72.12742295648351</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>32.4492060621888</v>
+        <v>32.66970268869157</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.5156414361929904</v>
+        <v>1.090330959729416</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>-0.7732575292050932</v>
+        <v>6.599392214839721</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6470</v>
+        <v>6449</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>宇智</t>
+          <t>鈺邦</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>529.719674221475</v>
+        <v>533.1466766103759</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>50</v>
+        <v>371</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.48938470220973</v>
+        <v>51.78281865712357</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>16.13833243339364</v>
+        <v>35.93020622556805</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.8120160995812797</v>
+        <v>1.651339635642737</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.0377163734908071</v>
+        <v>-10.26968174185765</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6414</v>
+        <v>6265</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>樺漢</t>
+          <t>方土昶</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>528.0401723156275</v>
+        <v>532.4245968299225</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>373.5</v>
+        <v>55</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,13 +2619,13 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>52.44596341235587</v>
+        <v>51.23046644998228</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>23.89946244908853</v>
+        <v>32.4492060621888</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.7414771903642228</v>
+        <v>0.5156414361929904</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>0</v>
@@ -2637,7 +2637,7 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>-3.18278985882522</v>
+        <v>-0.7732575292050932</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2647,21 +2647,21 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6462</v>
+        <v>6470</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>神盾</t>
+          <t>宇智</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>524.4785171032208</v>
+        <v>529.719674221475</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>124.5</v>
+        <v>50</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>53.09188804189217</v>
+        <v>57.48938470220973</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>21.81482239573661</v>
+        <v>16.13833243339364</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.781747395564374</v>
+        <v>0.8120160995812797</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.786519461204502</v>
+        <v>0.0377163734908071</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6274</v>
+        <v>6414</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>台燿</t>
+          <t>樺漢</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>514.6003279850353</v>
+        <v>528.0401723156275</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1700</v>
+        <v>373.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,13 +2725,13 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>56.35100260175481</v>
+        <v>52.44596341235587</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30.22420927453191</v>
+        <v>23.89946244908853</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.9934321955886164</v>
+        <v>0.7414771903642228</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-1.642049226877049</v>
+        <v>-3.18278985882522</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>6278</v>
+        <v>6462</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>台表科</t>
+          <t>神盾</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>487.6828481621196</v>
+        <v>524.4785171032208</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>205</v>
+        <v>124.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,13 +2778,13 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>50.95406884070198</v>
+        <v>53.09188804189217</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>20.70294452558156</v>
+        <v>21.81482239573661</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.7579971280184366</v>
+        <v>2.781747395564374</v>
       </c>
       <c r="K44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-1.983602587414885</v>
+        <v>1.786519461204502</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>6290</v>
+        <v>6274</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>良維</t>
+          <t>台燿</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>486.6656501645856</v>
+        <v>514.6003279850353</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>311.5</v>
+        <v>1700</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>51.57071410427282</v>
+        <v>56.35100260175481</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>14.07957415679771</v>
+        <v>30.22420927453191</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.5799992414263586</v>
+        <v>0.9934321955886164</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>-3.301026838099707</v>
+        <v>-1.642049226877049</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6170</v>
+        <v>6278</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>統振</t>
+          <t>台表科</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>482.9908454930114</v>
+        <v>487.6828481621196</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>52.7</v>
+        <v>205</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>57.25148689482506</v>
+        <v>50.95406884070198</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>14.76491557831792</v>
+        <v>20.70294452558156</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.340450034788977</v>
+        <v>0.7579971280184366</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>-0.0205213833222532</v>
+        <v>-1.983602587414885</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6263</v>
+        <v>6290</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>普萊德</t>
+          <t>良維</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>479.1616246210291</v>
+        <v>486.6656501645856</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>172</v>
+        <v>311.5</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>55.55254917277498</v>
+        <v>51.57071410427282</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15.96893553082346</v>
+        <v>14.07957415679771</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.493936500239967</v>
+        <v>0.5799992414263586</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>-0.0115243596103455</v>
+        <v>-3.301026838099707</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6224</v>
+        <v>6170</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>聚鼎</t>
+          <t>統振</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>469.9350213836963</v>
+        <v>482.9908454930114</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>79</v>
+        <v>52.7</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>50.04764239295256</v>
+        <v>57.25148689482506</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>22.99686899970392</v>
+        <v>14.76491557831792</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.2874049129964535</v>
+        <v>1.340450034788977</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.7179757076628093</v>
+        <v>-0.0205213833222532</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>6269</v>
+        <v>6263</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>台郡</t>
+          <t>普萊德</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>463.3823363281823</v>
+        <v>479.1616246210291</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>75.90000000000001</v>
+        <v>172</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>54.63684927661414</v>
+        <v>55.55254917277498</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>32.36725253698462</v>
+        <v>15.96893553082346</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.8752849207425328</v>
+        <v>2.493936500239967</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>0.6250615138173226</v>
+        <v>-0.0115243596103455</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>6177</v>
+        <v>6224</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>達麗</t>
+          <t>聚鼎</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>459.9763263979878</v>
+        <v>469.9350213836963</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>46</v>
+        <v>79</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,13 +3096,13 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>50.36915489245532</v>
+        <v>50.04764239295256</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>22.5158147143854</v>
+        <v>22.99686899970392</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.254636951737655</v>
+        <v>0.2874049129964535</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.0117903409115309</v>
+        <v>-0.7179757076628093</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6164</v>
+        <v>6269</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華興</t>
+          <t>台郡</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>459.9648154349225</v>
+        <v>463.3823363281823</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>13.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,13 +3149,13 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.03489782104426</v>
+        <v>54.63684927661414</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.41988740103306</v>
+        <v>32.36725253698462</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.9654708975117124</v>
+        <v>0.8752849207425328</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>0.0525969777467071</v>
+        <v>0.6250615138173226</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>6282</v>
+        <v>6177</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>康舒</t>
+          <t>達麗</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>459.4623297297142</v>
+        <v>459.9763263979878</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>58.7</v>
+        <v>46</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>49.84264410994806</v>
+        <v>50.36915489245532</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>31.86727264585681</v>
+        <v>22.5158147143854</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.6649941605012488</v>
+        <v>0.254636951737655</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>-0.3952146361032236</v>
+        <v>0.0117903409115309</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6284</v>
+        <v>6164</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>佳邦</t>
+          <t>華興</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>456.6463853749494</v>
+        <v>459.9648154349225</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>102</v>
+        <v>13.3</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,13 +3255,13 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>51.0361978152467</v>
+        <v>55.03489782104426</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>39.42871468175133</v>
+        <v>23.41988740103306</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.3205147625560059</v>
+        <v>0.9654708975117124</v>
       </c>
       <c r="K53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.056038331611231</v>
+        <v>0.0525969777467071</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6229</v>
+        <v>6282</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>研通</t>
+          <t>康舒</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>455.7292238402522</v>
+        <v>459.4623297297142</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>27.7</v>
+        <v>58.7</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>54.95191572904859</v>
+        <v>49.84264410994806</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>14.87650805018597</v>
+        <v>31.86727264585681</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.08802379956913</v>
+        <v>0.6649941605012488</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.1353900900583211</v>
+        <v>-0.3952146361032236</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6285</v>
+        <v>6284</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>啟碁</t>
+          <t>佳邦</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>451.4523006642227</v>
+        <v>456.6463853749494</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>256.5</v>
+        <v>102</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>42.19483054020584</v>
+        <v>51.0361978152467</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>20.75982519020947</v>
+        <v>39.42871468175133</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.490781978720101</v>
+        <v>0.3205147625560059</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>-4.940455779864721</v>
+        <v>-1.056038331611231</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6246</v>
+        <v>6229</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>臺龍</t>
+          <t>研通</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>449</v>
+        <v>455.7292238402522</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>16.1</v>
+        <v>27.7</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>57.04568323490458</v>
+        <v>54.95191572904859</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>21.87703677916338</v>
+        <v>14.87650805018597</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>9.63792021236724</v>
+        <v>1.08802379956913</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>0.0727036872815837</v>
+        <v>0.1353900900583211</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6279</v>
+        <v>6285</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>胡連</t>
+          <t>啟碁</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>448.0188728223998</v>
+        <v>451.4523006642227</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>119</v>
+        <v>256.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>50.16127577703892</v>
+        <v>42.19483054020584</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>18.37848313735305</v>
+        <v>20.75982519020947</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.3371292521291</v>
+        <v>0.490781978720101</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-0.3645932119511115</v>
+        <v>-4.940455779864721</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6217</v>
+        <v>6246</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>中探針</t>
+          <t>臺龍</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>437.6998871032782</v>
+        <v>449</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>275</v>
+        <v>16.1</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>54.19987106447827</v>
+        <v>57.04568323490458</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>14.9408000431574</v>
+        <v>21.87703677916338</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.313848333557166</v>
+        <v>9.63792021236724</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.389202974634051</v>
+        <v>0.0727036872815837</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6275</v>
+        <v>6279</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>元山</t>
+          <t>胡連</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>437.1587843176998</v>
+        <v>448.0188728223998</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,13 +3573,13 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>51.7587566736124</v>
+        <v>50.16127577703892</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>20.45253323770407</v>
+        <v>18.37848313735305</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.8289016168187961</v>
+        <v>0.3371292521291</v>
       </c>
       <c r="K59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.4181337923130764</v>
+        <v>-0.3645932119511115</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6244</v>
+        <v>6217</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>茂迪</t>
+          <t>中探針</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>434.0090329232246</v>
+        <v>437.6998871032782</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>27.55</v>
+        <v>275</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,13 +3626,13 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>43.56262917854372</v>
+        <v>54.19987106447827</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>17.46740830411807</v>
+        <v>14.9408000431574</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.3355787574882331</v>
+        <v>1.313848333557166</v>
       </c>
       <c r="K60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.3254931165762044</v>
+        <v>2.389202974634051</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6405</v>
+        <v>6275</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>悅城</t>
+          <t>元山</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>432.7969702776536</v>
+        <v>437.1587843176998</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>65.3</v>
+        <v>50</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>48.48419545542408</v>
+        <v>51.7587566736124</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>29.46730297883583</v>
+        <v>20.45253323770407</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.8939770679257708</v>
+        <v>0.8289016168187961</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>-1.372940424112898</v>
+        <v>0.4181337923130764</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>6214</v>
+        <v>6244</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>精誠</t>
+          <t>茂迪</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>419.9189172867278</v>
+        <v>434.0090329232246</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>129.5</v>
+        <v>27.55</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>41.12159399259541</v>
+        <v>43.56262917854372</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>20.52172285800859</v>
+        <v>17.46740830411807</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.2968989850920935</v>
+        <v>0.3355787574882331</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-2.391974084532551</v>
+        <v>-0.3254931165762044</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6291</v>
+        <v>6405</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沛亨</t>
+          <t>悅城</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>415.992532222942</v>
+        <v>432.7969702776536</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>594</v>
+        <v>65.3</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>56.38683345083507</v>
+        <v>48.48419545542408</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>18.62129908175565</v>
+        <v>29.46730297883583</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.27762874620155</v>
+        <v>0.8939770679257708</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-2.459690241323067</v>
+        <v>-1.372940424112898</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6222</v>
+        <v>6214</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>立軒</t>
+          <t>精誠</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>408.3814963406357</v>
+        <v>419.9189172867278</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>20.95</v>
+        <v>129.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>52.72697772434877</v>
+        <v>41.12159399259541</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>26.67933937197605</v>
+        <v>20.52172285800859</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2.133876103870523</v>
+        <v>0.2968989850920935</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.0878030400998854</v>
+        <v>-2.391974084532551</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6218</v>
+        <v>6291</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>豪勉</t>
+          <t>沛亨</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>403.5420254486488</v>
+        <v>415.992532222942</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>40.15</v>
+        <v>594</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>60.46789559267306</v>
+        <v>56.38683345083507</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>15.8215595236028</v>
+        <v>18.62129908175565</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.011871611971832</v>
+        <v>1.27762874620155</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6579590682320644</v>
+        <v>-2.459690241323067</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6228</v>
+        <v>6222</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>全譜</t>
+          <t>立軒</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>391.3021372876516</v>
+        <v>408.3814963406357</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>20</v>
+        <v>20.95</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>46.44228087192189</v>
+        <v>52.72697772434877</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>3.892310625842884</v>
+        <v>26.67933937197605</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>3.02801034082015</v>
+        <v>2.133876103870523</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-0.0642965347621431</v>
+        <v>0.0878030400998854</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6464</v>
+        <v>6218</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>台數科</t>
+          <t>豪勉</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>379.2999064471281</v>
+        <v>403.5420254486488</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>40.15</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>38.4045450576293</v>
+        <v>60.46789559267306</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15.04748949423473</v>
+        <v>15.8215595236028</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.2572652830936733</v>
+        <v>1.011871611971832</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1058121099806991</v>
+        <v>0.6579590682320644</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6206</v>
+        <v>6228</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>飛捷</t>
+          <t>全譜</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>372.757463824105</v>
+        <v>391.3021372876516</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>129.5</v>
+        <v>20</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>46.32600982984209</v>
+        <v>46.44228087192189</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>17.37168144910499</v>
+        <v>3.892310625842884</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.3071505090531691</v>
+        <v>3.02801034082015</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-1.328292136507408</v>
+        <v>-0.0642965347621431</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6225</v>
+        <v>6187</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>天瀚</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>372.0756105666599</v>
+        <v>390.876862879049</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>21.5</v>
+        <v>1105</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.95537317512452</v>
+        <v>48.52365064355637</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.1572951081273</v>
+        <v>11.73921040597623</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.045105404070599</v>
+        <v>0.2584678397129277</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-0.3378872015353455</v>
+        <v>-0.3572644494786416</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6419</v>
+        <v>6464</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>京晨科</t>
+          <t>台數科</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>363.7254345977909</v>
+        <v>379.2999064471281</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>148</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,13 +4156,13 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.21143562242665</v>
+        <v>38.4045450576293</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>14.2686738379403</v>
+        <v>15.04748949423473</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.721489530064527</v>
+        <v>0.2572652830936733</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.083557878164894</v>
+        <v>-0.1058121099806991</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6233</v>
+        <v>6206</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>旺玖</t>
+          <t>飛捷</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>356.040021279951</v>
+        <v>372.757463824105</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>25.95</v>
+        <v>129.5</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>53.64648474133021</v>
+        <v>46.32600982984209</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15.09553192456551</v>
+        <v>17.37168144910499</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.544688413185322</v>
+        <v>0.3071505090531691</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.335277953713559</v>
+        <v>-1.328292136507408</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>6227</v>
+        <v>6225</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>茂綸</t>
+          <t>天瀚</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>351.5885817961376</v>
+        <v>372.0756105666599</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>121.5</v>
+        <v>21.5</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>49.4138015630446</v>
+        <v>41.95537317512452</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>19.81246506585339</v>
+        <v>12.1572951081273</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.2504924098417596</v>
+        <v>1.045105404070599</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-2.04302013916798</v>
+        <v>-0.3378872015353455</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6438</v>
+        <v>6419</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>迅得</t>
+          <t>京晨科</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>350.4050871605575</v>
+        <v>363.7254345977909</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>42.3357718174035</v>
+        <v>52.21143562242665</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>24.54208610147206</v>
+        <v>14.2686738379403</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.3853978649729627</v>
+        <v>0.721489530064527</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.5257104652254609</v>
+        <v>1.083557878164894</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6215</v>
+        <v>6233</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>和椿</t>
+          <t>旺玖</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>346.9662225836487</v>
+        <v>356.040021279951</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>105.5</v>
+        <v>25.95</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>39.45690104984959</v>
+        <v>53.64648474133021</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>19.58648884709861</v>
+        <v>15.09553192456551</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.3928194909063793</v>
+        <v>1.544688413185322</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.8630989434218712</v>
+        <v>0.335277953713559</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>6234</v>
+        <v>6227</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>高僑</t>
+          <t>茂綸</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>344.8005092646731</v>
+        <v>351.5885817961376</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.75</v>
+        <v>121.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>54.21448854024788</v>
+        <v>49.4138015630446</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>15.8988280098138</v>
+        <v>19.81246506585339</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.433990179257872</v>
+        <v>0.2504924098417596</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>0.404520881424422</v>
+        <v>-2.04302013916798</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>6261</v>
+        <v>6438</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>久元</t>
+          <t>迅得</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>340.7452253554504</v>
+        <v>350.4050871605575</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>42.10098652729511</v>
+        <v>42.3357718174035</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>20.82159524650269</v>
+        <v>24.54208610147206</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.445145635350083</v>
+        <v>0.3853978649729627</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,7 +4492,7 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.5866536892320733</v>
+        <v>0.5257104652254609</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6423</v>
+        <v>6215</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>億而得-創</t>
+          <t>和椿</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>307.830482320141</v>
+        <v>346.9662225836487</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>81.90000000000001</v>
+        <v>105.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>37.71840129060428</v>
+        <v>39.45690104984959</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>26.95035401305896</v>
+        <v>19.58648884709861</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4221713312093553</v>
+        <v>0.3928194909063793</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2906624872840746</v>
+        <v>-0.8630989434218712</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6205</v>
+        <v>6234</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>詮欣</t>
+          <t>高僑</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>307.5739802551028</v>
+        <v>344.8005092646731</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>78.3</v>
+        <v>48.75</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.18995849129775</v>
+        <v>54.21448854024788</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>11.9189784888783</v>
+        <v>15.8988280098138</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.2503022874610298</v>
+        <v>1.433990179257872</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.5019729293354366</v>
+        <v>0.404520881424422</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6191</v>
+        <v>6261</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>精成科</t>
+          <t>久元</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>303.9724532656035</v>
+        <v>340.7452253554504</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>99.3</v>
+        <v>96</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>51.68895916950135</v>
+        <v>42.10098652729511</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>17.72393900412237</v>
+        <v>20.82159524650269</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6193428467370474</v>
+        <v>0.445145635350083</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.2967516878927094</v>
+        <v>-0.5866536892320733</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6210</v>
+        <v>6423</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>慶生</t>
+          <t>億而得-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>302.0058468686109</v>
+        <v>307.830482320141</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>20.4</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>44.13513547773184</v>
+        <v>37.71840129060428</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>16.83998723944522</v>
+        <v>26.95035401305896</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>1.186393741133298</v>
+        <v>0.4221713312093553</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0881730159520622</v>
+        <v>0.2906624872840746</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6418</v>
+        <v>6205</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>詠昇</t>
+          <t>詮欣</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>296.7199445658796</v>
+        <v>307.5739802551028</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>31.05</v>
+        <v>78.3</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>47.05851348746867</v>
+        <v>46.18995849129775</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>22.65446867577272</v>
+        <v>11.9189784888783</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.1980375033521973</v>
+        <v>0.2503022874610298</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-0.1174229236330605</v>
+        <v>-0.5019729293354366</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6167</v>
+        <v>6191</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>久正</t>
+          <t>精成科</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>288.1126191936493</v>
+        <v>303.9724532656035</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>12.05</v>
+        <v>99.3</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>50.5107251833526</v>
+        <v>51.68895916950135</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>11.9734115932841</v>
+        <v>17.72393900412237</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.9948826678521724</v>
+        <v>0.6193428467370474</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0763464701189808</v>
+        <v>0.2967516878927094</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6416</v>
+        <v>6210</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>瑞祺電通</t>
+          <t>慶生</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>285.3559377191485</v>
+        <v>302.0058468686109</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>81.2</v>
+        <v>20.4</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.53791421387714</v>
+        <v>44.13513547773184</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>22.05264236581927</v>
+        <v>16.83998723944522</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.8490406588556071</v>
+        <v>1.186393741133298</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.519696795737821</v>
+        <v>-0.0881730159520622</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6442</v>
+        <v>6418</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>詠昇</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>282.5313548171704</v>
+        <v>296.7199445658796</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>1865</v>
+        <v>31.05</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>46.55817294786824</v>
+        <v>47.05851348746867</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>11.1601850231349</v>
+        <v>22.65446867577272</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.079053924557613</v>
+        <v>0.1980375033521973</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-1.424664583573723</v>
+        <v>-0.1174229236330605</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6245</v>
+        <v>6167</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>立端</t>
+          <t>久正</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>281.8095048630987</v>
+        <v>288.1126191936493</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>79.7</v>
+        <v>12.05</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>39.85789981356189</v>
+        <v>50.5107251833526</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.04867878924759</v>
+        <v>11.9734115932841</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4579659695838693</v>
+        <v>0.9948826678521724</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>-0.7586841805792159</v>
+        <v>0.0763464701189808</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>6456</v>
+        <v>6416</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>GIS-KY</t>
+          <t>瑞祺電通</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>281.6903916581454</v>
+        <v>285.3559377191485</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>71.5</v>
+        <v>81.2</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>46.48796512599508</v>
+        <v>38.53791421387714</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>11.6783541077115</v>
+        <v>22.05264236581927</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.3166400436865836</v>
+        <v>0.8490406588556071</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.7378177214707118</v>
+        <v>-0.519696795737821</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>6283</v>
+        <v>6442</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>淳安</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>272.3963724424429</v>
+        <v>282.5313548171704</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>24.35</v>
+        <v>1865</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>51.85617019796062</v>
+        <v>46.55817294786824</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>16.32652446834546</v>
+        <v>11.1601850231349</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8507160389707513</v>
+        <v>1.079053924557613</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0380206281164508</v>
+        <v>-1.424664583573723</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6277</v>
+        <v>6245</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>宏正</t>
+          <t>立端</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>271.9416077785245</v>
+        <v>281.8095048630987</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>71.2</v>
+        <v>79.7</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>40.24900311064633</v>
+        <v>39.85789981356189</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>29.81836497577659</v>
+        <v>17.04867878924759</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.2316644204445606</v>
+        <v>0.4579659695838693</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.6846096535186212</v>
+        <v>-0.7586841805792159</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>6417</v>
+        <v>6456</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>韋僑</t>
+          <t>GIS-KY</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>268.8271492727269</v>
+        <v>281.6903916581454</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>131.5</v>
+        <v>71.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>48.64716895916205</v>
+        <v>46.48796512599508</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>14.90358910323537</v>
+        <v>11.6783541077115</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.3403659514213538</v>
+        <v>0.3166400436865836</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-1.094598710096087</v>
+        <v>-0.7378177214707118</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6281</v>
+        <v>6283</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>全國電</t>
+          <t>淳安</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>259.1090023488516</v>
+        <v>272.3963724424429</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>51.3</v>
+        <v>24.35</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>49.16877191846371</v>
+        <v>51.85617019796062</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>11.30515831075484</v>
+        <v>16.32652446834546</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.4865711334190608</v>
+        <v>0.8507160389707513</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>0.0202804162296955</v>
+        <v>-0.0380206281164508</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>6412</v>
+        <v>6277</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>群電</t>
+          <t>宏正</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>255.6455178810062</v>
+        <v>271.9416077785245</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>48.71899604962299</v>
+        <v>40.24900311064633</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>18.62719949679865</v>
+        <v>29.81836497577659</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.3223642358490702</v>
+        <v>0.2316644204445606</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.5525031388305102</v>
+        <v>-0.6846096535186212</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6216</v>
+        <v>6417</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>居易</t>
+          <t>韋僑</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>245.167878647877</v>
+        <v>268.8271492727269</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>23.25</v>
+        <v>131.5</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>52.33393250024849</v>
+        <v>48.64716895916205</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>14.86685040397176</v>
+        <v>14.90358910323537</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.4126288731326872</v>
+        <v>0.3403659514213538</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0864011701758422</v>
+        <v>-1.094598710096087</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6176</v>
+        <v>6281</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>瑞儀</t>
+          <t>全國電</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>242.4599700909561</v>
+        <v>259.1090023488516</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>90.7</v>
+        <v>51.3</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>40.24086124291955</v>
+        <v>49.16877191846371</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>24.111071868088</v>
+        <v>11.30515831075484</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.9164086757621572</v>
+        <v>0.4865711334190608</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.222421538799491</v>
+        <v>0.0202804162296955</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6184</v>
+        <v>6412</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>大豐電</t>
+          <t>群電</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>238.3776687976379</v>
+        <v>255.6455178810062</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>44.05</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>24.22294329248543</v>
+        <v>48.71899604962299</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>30.25186408264606</v>
+        <v>18.62719949679865</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.482469558963118</v>
+        <v>0.3223642358490702</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.2183263885659729</v>
+        <v>-0.5525031388305102</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6230</v>
+        <v>6216</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>尼得科超眾</t>
+          <t>居易</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>236.5388914303448</v>
+        <v>245.167878647877</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>129</v>
+        <v>23.25</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>39.30388554995242</v>
+        <v>52.33393250024849</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>10.96491040706828</v>
+        <v>14.86685040397176</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.8069106978521485</v>
+        <v>0.4126288731326872</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0657863478718967</v>
+        <v>0.0864011701758422</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>6485</v>
+        <v>6176</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>點序</t>
+          <t>瑞儀</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>234.6859863894718</v>
+        <v>242.4599700909561</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>86.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>41.29806209673674</v>
+        <v>40.24086124291955</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>17.82578115035419</v>
+        <v>24.111071868088</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.2350242673184213</v>
+        <v>0.9164086757621572</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-1.626719559218161</v>
+        <v>-0.222421538799491</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>6192</v>
+        <v>6184</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>巨路</t>
+          <t>大豐電</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>224.5355199030748</v>
+        <v>238.3776687976379</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>122.5</v>
+        <v>44.05</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>49.27253001550284</v>
+        <v>24.22294329248543</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>22.82999295314595</v>
+        <v>30.25186408264606</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.5580248292165785</v>
+        <v>1.482469558963118</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-0.2417033626151745</v>
+        <v>-0.2183263885659729</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6198</v>
+        <v>6230</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>瑞築</t>
+          <t>尼得科超眾</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>219.2326584233064</v>
+        <v>236.5388914303448</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>20.65</v>
+        <v>129</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>51.20636422762262</v>
+        <v>39.30388554995242</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7.38669166423947</v>
+        <v>10.96491040706828</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.2018808566477683</v>
+        <v>0.8069106978521485</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.3051322818481325</v>
+        <v>-0.0657863478718967</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6474</v>
+        <v>6485</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>華豫寧</t>
+          <t>點序</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>211.0319561666172</v>
+        <v>234.6859863894718</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>37.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>51.29565493733026</v>
+        <v>41.29806209673674</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>16.58874546228031</v>
+        <v>17.82578115035419</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.316423921830017</v>
+        <v>0.2350242673184213</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.5161469500980934</v>
+        <v>-1.626719559218161</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6443</v>
+        <v>6192</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>元晶</t>
+          <t>巨路</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>208.8142057073485</v>
+        <v>224.5355199030748</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>36.4</v>
+        <v>122.5</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>39.5946739469842</v>
+        <v>49.27253001550284</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>16.15653863023201</v>
+        <v>22.82999295314595</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.2989868314176727</v>
+        <v>0.5580248292165785</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-0.4568127278321842</v>
+        <v>-0.2417033626151745</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6426</v>
+        <v>6198</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>統新</t>
+          <t>瑞築</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>207.1673377660791</v>
+        <v>219.2326584233064</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>214</v>
+        <v>20.65</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.77786954274709</v>
+        <v>51.20636422762262</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>16.99681771744708</v>
+        <v>7.38669166423947</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.5938820979250913</v>
+        <v>0.2018808566477683</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>-0.5566792881450837</v>
+        <v>0.3051322818481325</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6266</v>
+        <v>6474</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>泰詠</t>
+          <t>華豫寧</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>199.6173721573606</v>
+        <v>211.0319561666172</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>25.45</v>
+        <v>37.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,13 +5852,13 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>34.7917927367799</v>
+        <v>51.29565493733026</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>23.05824406600973</v>
+        <v>16.58874546228031</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.4649462753226985</v>
+        <v>1.316423921830017</v>
       </c>
       <c r="K102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.1127674536722683</v>
+        <v>0.5161469500980934</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6165</v>
+        <v>6443</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>浪凡</t>
+          <t>元晶</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>198.6188329323653</v>
+        <v>208.8142057073485</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>47.55</v>
+        <v>36.4</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>43.80793497558122</v>
+        <v>39.5946739469842</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15.71514507360965</v>
+        <v>16.15653863023201</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7263000424492719</v>
+        <v>0.2989868314176727</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-0.1763617072383451</v>
+        <v>-0.4568127278321842</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6272</v>
+        <v>6426</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>驊陞</t>
+          <t>統新</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>191.124285050723</v>
+        <v>207.1673377660791</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>31.5</v>
+        <v>214</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>37.71152872882634</v>
+        <v>45.77786954274709</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>25.2504594495061</v>
+        <v>16.99681771744708</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4837948135883864</v>
+        <v>0.5938820979250913</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.5804838463212214</v>
+        <v>-0.5566792881450837</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6276</v>
+        <v>6266</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>安鈦克</t>
+          <t>泰詠</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>191.0664603599481</v>
+        <v>199.6173721573606</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>21.8</v>
+        <v>25.45</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>24.51363289048662</v>
+        <v>34.7917927367799</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>26.54104618813055</v>
+        <v>23.05824406600973</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.9301935443785144</v>
+        <v>0.4649462753226985</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,7 +6029,7 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.2734481457745066</v>
+        <v>-0.1127674536722683</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6235</v>
+        <v>6165</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>華孚</t>
+          <t>浪凡</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>164.5750930145484</v>
+        <v>198.6188329323653</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>40.2</v>
+        <v>47.55</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>41.96805456044704</v>
+        <v>43.80793497558122</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>13.37944149230596</v>
+        <v>15.71514507360965</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.2810951417048624</v>
+        <v>0.7263000424492719</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>-0.129003773051275</v>
+        <v>-0.1763617072383451</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6183</v>
+        <v>6272</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>關貿</t>
+          <t>驊陞</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>159.5163046241514</v>
+        <v>191.124285050723</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>90.09999999999999</v>
+        <v>31.5</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.98230655134921</v>
+        <v>37.71152872882634</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>13.95505686181788</v>
+        <v>25.2504594495061</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.6457650371868005</v>
+        <v>0.4837948135883864</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1433889681960271</v>
+        <v>-0.5804838463212214</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>6201</v>
+        <v>6276</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>亞弘電</t>
+          <t>安鈦克</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>157.8010700239977</v>
+        <v>191.0664603599481</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>48.2</v>
+        <v>21.8</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>48.10107918661072</v>
+        <v>24.51363289048662</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>15.1186788923802</v>
+        <v>26.54104618813055</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.9053518962720204</v>
+        <v>0.9301935443785144</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1514921099211265</v>
+        <v>-0.2734481457745066</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6441</v>
+        <v>6235</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>廣錠</t>
+          <t>華孚</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>153.921148472681</v>
+        <v>164.5750930145484</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>22.05</v>
+        <v>40.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>41.32225436315269</v>
+        <v>41.96805456044704</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>10.42410703519122</v>
+        <v>13.37944149230596</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.3811857136001577</v>
+        <v>0.2810951417048624</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.124025194084294</v>
+        <v>-0.129003773051275</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>6188</v>
+        <v>6183</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>廣明</t>
+          <t>關貿</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>146.5205380084524</v>
+        <v>159.5163046241514</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>77.09999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.42710616271431</v>
+        <v>45.98230655134921</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>14.5294180572725</v>
+        <v>13.95505686181788</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.7740509406515547</v>
+        <v>0.6457650371868005</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,48 +6294,48 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.3202228049585294</v>
+        <v>0.1433889681960271</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6287</v>
+        <v>6201</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>元隆</t>
+          <t>亞弘電</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>141.298140145067</v>
+        <v>157.8010700239977</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>8.890000000000001</v>
+        <v>48.2</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>2025-06-20</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G111" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>14.26499549787847</v>
+        <v>48.10107918661072</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>0.9122007574990488</v>
+        <v>15.1186788923802</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.3819364013941486</v>
+        <v>0.9053518962720204</v>
       </c>
       <c r="K111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.0153085825903483</v>
+        <v>0.1514921099211265</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>6477</v>
+        <v>6441</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>安集</t>
+          <t>廣錠</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>124.8610763885456</v>
+        <v>153.921148472681</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>31.1</v>
+        <v>22.05</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>39.29373568189126</v>
+        <v>41.32225436315269</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.30947438371686</v>
+        <v>10.42410703519122</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.7521347407755462</v>
+        <v>0.3811857136001577</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.1653747227307607</v>
+        <v>-0.124025194084294</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6236</v>
+        <v>6188</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>中湛</t>
+          <t>廣明</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>108.542494500482</v>
+        <v>146.5205380084524</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>0</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>48.02625878184231</v>
+        <v>38.42710616271431</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7.051586276139469</v>
+        <v>14.5294180572725</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0</v>
+        <v>0.7740509406515547</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,48 +6453,48 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.3018003871133936</v>
+        <v>-0.3202228049585294</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6203</v>
+        <v>6287</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>海韻電</t>
+          <t>元隆</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>95.33460311027444</v>
+        <v>141.298140145067</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>67.09999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2025-06-20</t>
         </is>
       </c>
       <c r="G114" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>42.37686124657303</v>
+        <v>14.26499549787847</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.9957187727363</v>
+        <v>0.9122007574990488</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.406016603786831</v>
+        <v>0.3819364013941486</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>0</v>
@@ -6506,62 +6506,221 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.2300405950044747</v>
+        <v>-0.0153085825903483</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
+        <v>6477</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>安集</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>124.8610763885456</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>31.1</v>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>39.29373568189126</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>13.30947438371686</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.7521347407755462</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N115" s="2" t="n">
+        <v>-0.1653747227307607</v>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>6236</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>中湛</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>108.542494500482</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>48.02625878184231</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>7.051586276139469</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N116" s="2" t="n">
+        <v>-0.3018003871133936</v>
+      </c>
+      <c r="O116" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, obv_uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>6203</v>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>海韻電</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>95.33460311027444</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>42.37686124657303</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>18.9957187727363</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>0.406016603786831</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N117" s="2" t="n">
+        <v>-0.2300405950044747</v>
+      </c>
+      <c r="O117" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
         <v>6194</v>
       </c>
-      <c r="B115" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>育富</t>
         </is>
       </c>
-      <c r="C115" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D115" s="2" t="n">
+      <c r="C118" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>83.94121120500074</v>
       </c>
-      <c r="E115" s="2" t="n">
+      <c r="E118" s="2" t="n">
         <v>32.25</v>
       </c>
-      <c r="F115" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G115" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H115" s="2" t="n">
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H118" s="2" t="n">
         <v>42.86682362546305</v>
       </c>
-      <c r="I115" s="2" t="n">
+      <c r="I118" s="2" t="n">
         <v>15.73879530205949</v>
       </c>
-      <c r="J115" s="2" t="n">
+      <c r="J118" s="2" t="n">
         <v>0.5142866202941356</v>
       </c>
-      <c r="K115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N115" s="2" t="n">
+      <c r="K118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N118" s="2" t="n">
         <v>-0.1075174398862669</v>
       </c>
-      <c r="O115" s="2" t="inlineStr">
+      <c r="O118" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
